--- a/public/database/Write Essay/ESSAY/Essay.xlsx
+++ b/public/database/Write Essay/ESSAY/Essay.xlsx
@@ -7809,7 +7809,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>#370 WE 论点翻译 2</t>
+          <t>The Role of Examinations in Education</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
